--- a/artfynd/A 1503-2024 artfynd.xlsx
+++ b/artfynd/A 1503-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114745725</v>
+        <v>114745714</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>328030</v>
+        <v>327975</v>
       </c>
       <c r="R2" t="n">
-        <v>6417366</v>
+        <v>6417480</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -773,38 +772,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114745752</v>
+        <v>114745744</v>
       </c>
       <c r="B3" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -836,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>328089</v>
+        <v>328030</v>
       </c>
       <c r="R3" t="n">
-        <v>6417363</v>
+        <v>6417366</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,31 +889,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114745744</v>
+        <v>114745752</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -952,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>328030</v>
+        <v>328089</v>
       </c>
       <c r="R4" t="n">
-        <v>6417366</v>
+        <v>6417363</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,59 +1000,50 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114745714</v>
+        <v>114745725</v>
       </c>
       <c r="B5" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1072,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>327975</v>
+        <v>328030</v>
       </c>
       <c r="R5" t="n">
-        <v>6417480</v>
+        <v>6417366</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,18 +1105,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 1503-2024 artfynd.xlsx
+++ b/artfynd/A 1503-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114745714</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114745744</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114745752</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,8 +1141,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114745725</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>